--- a/test_data/UltraArm_P1.xlsx
+++ b/test_data/UltraArm_P1.xlsx
@@ -4,16 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="5" activeTab="9"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="14" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
-    <sheet name="get_modified_version" sheetId="3" r:id="rId2"/>
+    <sheet name="get_modify_version" sheetId="3" r:id="rId2"/>
     <sheet name="set_angles" sheetId="19" r:id="rId3"/>
     <sheet name="set_angle" sheetId="21" r:id="rId4"/>
-    <sheet name="get_error_information" sheetId="11" r:id="rId5"/>
-    <sheet name="get_angles" sheetId="18" r:id="rId6"/>
-    <sheet name="set_coords" sheetId="23" r:id="rId7"/>
+    <sheet name="get_angles_info" sheetId="18" r:id="rId5"/>
+    <sheet name="set_coords" sheetId="23" r:id="rId6"/>
+    <sheet name="get_error_information" sheetId="11" r:id="rId7"/>
     <sheet name="get_coords" sheetId="22" r:id="rId8"/>
     <sheet name="send_coord" sheetId="24" r:id="rId9"/>
     <sheet name="set_jog_angle" sheetId="31" r:id="rId10"/>
@@ -25,6 +25,9 @@
     <sheet name="jog_increment_coord" sheetId="35" r:id="rId16"/>
     <sheet name="set_servo_calibration" sheetId="45" r:id="rId17"/>
     <sheet name="set_base_io_output" sheetId="52" r:id="rId18"/>
+    <sheet name="set_joint_enable" sheetId="53" r:id="rId19"/>
+    <sheet name="set_joint_release" sheetId="54" r:id="rId20"/>
+    <sheet name="Sheet3" sheetId="55" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="268">
   <si>
     <t>ID</t>
   </si>
@@ -76,7 +79,7 @@
     <t>正确获取修正版本号</t>
   </si>
   <si>
-    <t>get_modified_version</t>
+    <t>get_modify_version</t>
   </si>
   <si>
     <t>angles</t>
@@ -91,25 +94,25 @@
     <t>set_angles</t>
   </si>
   <si>
-    <t>[-160,0,0,0]</t>
+    <t>[-160,0,90,0]</t>
   </si>
   <si>
     <t>使一关节运动到正限位</t>
   </si>
   <si>
-    <t>[160,0,0,0]</t>
+    <t>[160,0,90,0]</t>
   </si>
   <si>
     <t>使二关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,-20,0,0]</t>
+    <t>[0,-20,90,0]</t>
   </si>
   <si>
     <t>使二关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,85,0,0]</t>
+    <t>[0,85,90,0]</t>
   </si>
   <si>
     <t>使三关节运动到负限位</t>
@@ -127,31 +130,31 @@
     <t>使四关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,0,0,180]</t>
+    <t>[0,0,90,180]</t>
   </si>
   <si>
     <t>使四关节运动到正限位</t>
   </si>
   <si>
-    <t>[0,0,0,-180]</t>
+    <t>[0,0,90,-180]</t>
   </si>
   <si>
     <t>全关节运动，角度超限</t>
   </si>
   <si>
-    <t>[-161,0,0,0]</t>
+    <t>[-161,0,90,0]</t>
   </si>
   <si>
     <t>exception</t>
   </si>
   <si>
-    <t>[161,0,0,0]</t>
-  </si>
-  <si>
-    <t>[0,-21,0,0]</t>
-  </si>
-  <si>
-    <t>[0,86,0,0]</t>
+    <t>[161,0,90,0]</t>
+  </si>
+  <si>
+    <t>[0,-21,90,0]</t>
+  </si>
+  <si>
+    <t>[0,86,90,0]</t>
   </si>
   <si>
     <t>[0,0,91,0]</t>
@@ -160,10 +163,10 @@
     <t>[0,0,201,0]</t>
   </si>
   <si>
-    <t>[0,0,0,181]</t>
-  </si>
-  <si>
-    <t>[0,0,0,-181]</t>
+    <t>[0,0,90,181]</t>
+  </si>
+  <si>
+    <t>[0,0,90,-181]</t>
   </si>
   <si>
     <t>全关节运动，速度超限</t>
@@ -193,6 +196,102 @@
     <t>设置速度超限</t>
   </si>
   <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>读取全角度</t>
+  </si>
+  <si>
+    <t>get_angles_info</t>
+  </si>
+  <si>
+    <t>[10,10,90,10]</t>
+  </si>
+  <si>
+    <t>[20,20,90,20]</t>
+  </si>
+  <si>
+    <t>coords</t>
+  </si>
+  <si>
+    <t>运动x轴（正向）</t>
+  </si>
+  <si>
+    <t>send_coords</t>
+  </si>
+  <si>
+    <t>[100,0.00,231.00,0.00]</t>
+  </si>
+  <si>
+    <t>运动x轴（反向）</t>
+  </si>
+  <si>
+    <t>[60,0.00,231.00,0.00]</t>
+  </si>
+  <si>
+    <t>运动y轴（正向）</t>
+  </si>
+  <si>
+    <t>[83.50,30,231.00,0.00]</t>
+  </si>
+  <si>
+    <t>运动y轴（反向）</t>
+  </si>
+  <si>
+    <t>[83.50,-30,231.00,0.00]</t>
+  </si>
+  <si>
+    <t>运动z轴（正向）</t>
+  </si>
+  <si>
+    <t>[83.50,0.00,200,0.00]</t>
+  </si>
+  <si>
+    <t>运动z轴（反向）</t>
+  </si>
+  <si>
+    <t>[83.50,0.00,240,0.00]</t>
+  </si>
+  <si>
+    <t>运动rx轴（正向）</t>
+  </si>
+  <si>
+    <t>[83.50,0.00,231.00,30]</t>
+  </si>
+  <si>
+    <t>运动rx轴（反向）</t>
+  </si>
+  <si>
+    <t>[83.50,0.00,231.00,-30]</t>
+  </si>
+  <si>
+    <t>全关节运动，坐标超限，x轴</t>
+  </si>
+  <si>
+    <t>[303,0.00,231.00,-30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>[364,0.00,231.00,-30]</t>
+  </si>
+  <si>
+    <t>全关节运动，坐标超限，Y轴</t>
+  </si>
+  <si>
+    <t>[83.50,364,231.00,-30]</t>
+  </si>
+  <si>
+    <t>[83.50,-364,231.00,-30]</t>
+  </si>
+  <si>
+    <t>全关节运动，坐标超限，Z轴</t>
+  </si>
+  <si>
+    <t>[83.50,0.00,-158,-30]</t>
+  </si>
+  <si>
     <t>target_angles</t>
   </si>
   <si>
@@ -226,105 +325,6 @@
     <t>[-8.75, -44.21, -7.2, 48.05, 8.98, 0.0]</t>
   </si>
   <si>
-    <t>parameter</t>
-  </si>
-  <si>
-    <t>读取全角度</t>
-  </si>
-  <si>
-    <t>get_angles</t>
-  </si>
-  <si>
-    <t>[10,10,10,10]</t>
-  </si>
-  <si>
-    <t>[20,20,20,20]</t>
-  </si>
-  <si>
-    <t>coords</t>
-  </si>
-  <si>
-    <t>运动x轴（正向）</t>
-  </si>
-  <si>
-    <t>send_coords</t>
-  </si>
-  <si>
-    <t>[200, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动x轴（反向）</t>
-  </si>
-  <si>
-    <t>[100, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动y轴（正向）</t>
-  </si>
-  <si>
-    <t>[149.9, -30, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动y轴（反向）</t>
-  </si>
-  <si>
-    <t>[149.9, -150, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动z轴（正向）</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 350, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动z轴（反向）</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 250, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动rx轴（正向）</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 298.4, -160, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>运动rx轴（反向）</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 298.4, 150, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>全关节运动，坐标超限，x轴</t>
-  </si>
-  <si>
-    <t>[-467, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>[467, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>全关节运动，坐标超限，Y轴</t>
-  </si>
-  <si>
-    <t>[149.9, -467, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>[149.9, 467, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>全关节运动，坐标超限，Z轴</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, -151, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 677, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
-    <t>[149.9, -86.8, 298.4, 179.99, 0.0, -90.0]</t>
-  </si>
-  <si>
     <t>读取全关节坐标</t>
   </si>
   <si>
@@ -839,6 +839,18 @@
   </si>
   <si>
     <t>设置引脚状态超限</t>
+  </si>
+  <si>
+    <t>设置夹爪上使能</t>
+  </si>
+  <si>
+    <t>set_joint_enable</t>
+  </si>
+  <si>
+    <t>设置夹爪掉使能</t>
+  </si>
+  <si>
+    <t>set_joint_release</t>
   </si>
 </sst>
 </file>
@@ -1870,10 +1882,10 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -1893,7 +1905,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -1922,7 +1934,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -1951,7 +1963,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -1980,7 +1992,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -2009,7 +2021,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -2038,7 +2050,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -2067,7 +2079,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -2096,7 +2108,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -2125,7 +2137,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -2152,7 +2164,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="2">
         <v>4</v>
@@ -2176,10 +2188,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2202,10 +2214,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2228,10 +2240,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -2254,10 +2266,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -2307,7 +2319,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -2321,10 +2333,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -2341,10 +2353,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -2361,10 +2373,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -2378,10 +2390,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -2422,7 +2434,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -2436,10 +2448,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -2454,17 +2466,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2500,10 +2512,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -2520,10 +2532,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2546,10 +2558,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -2572,10 +2584,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -2598,10 +2610,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -2624,10 +2636,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -2650,10 +2662,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -2676,10 +2688,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -2694,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2702,10 +2714,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -2720,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2728,10 +2740,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -2746,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2754,10 +2766,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -2772,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2780,10 +2792,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -2798,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2806,10 +2818,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -2824,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
@@ -2835,7 +2847,7 @@
         <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -2859,7 +2871,7 @@
         <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -2880,10 +2892,10 @@
         <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -2904,10 +2916,10 @@
         <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -2928,10 +2940,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -2952,10 +2964,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
@@ -3004,10 +3016,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -3024,10 +3036,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3050,10 +3062,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3076,10 +3088,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -3102,10 +3114,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -3128,10 +3140,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -3146,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3154,10 +3166,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -3180,10 +3192,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -3206,10 +3218,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -3232,10 +3244,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -3258,10 +3270,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -3284,10 +3296,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -3310,10 +3322,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -3336,10 +3348,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -3354,7 +3366,7 @@
         <v>-1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3362,10 +3374,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -3380,7 +3392,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3388,10 +3400,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -3406,7 +3418,7 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3414,10 +3426,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -3432,7 +3444,7 @@
         <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3440,10 +3452,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -3458,7 +3470,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3466,10 +3478,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -3484,7 +3496,7 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3492,10 +3504,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -3510,7 +3522,7 @@
         <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3518,10 +3530,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -3536,7 +3548,7 @@
         <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3544,10 +3556,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -3562,7 +3574,7 @@
         <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3570,10 +3582,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -3588,7 +3600,7 @@
         <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3596,10 +3608,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -3614,7 +3626,7 @@
         <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3622,10 +3634,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -3640,7 +3652,7 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:8">
@@ -3651,7 +3663,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -3675,7 +3687,7 @@
         <v>48</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -3696,10 +3708,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -3720,10 +3732,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -3744,10 +3756,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -3768,10 +3780,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -3823,7 +3835,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -3840,10 +3852,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3866,10 +3878,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3892,10 +3904,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -3918,10 +3930,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -3944,10 +3956,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -3970,10 +3982,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -3996,10 +4008,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -4022,10 +4034,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -4048,10 +4060,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -4074,10 +4086,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -4100,10 +4112,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -4126,10 +4138,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4152,10 +4164,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4170,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4178,10 +4190,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -4196,7 +4208,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4204,10 +4216,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -4222,7 +4234,7 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4230,10 +4242,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -4248,7 +4260,7 @@
         <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4256,10 +4268,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -4274,7 +4286,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4282,10 +4294,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -4300,7 +4312,7 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4308,10 +4320,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -4326,7 +4338,7 @@
         <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4334,10 +4346,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -4352,7 +4364,7 @@
         <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4360,10 +4372,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -4378,7 +4390,7 @@
         <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4386,10 +4398,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -4404,7 +4416,7 @@
         <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4412,10 +4424,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -4430,7 +4442,7 @@
         <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4438,10 +4450,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -4456,7 +4468,7 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4467,7 +4479,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -4491,7 +4503,7 @@
         <v>48</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -4512,10 +4524,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -4536,10 +4548,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -4560,10 +4572,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -4584,10 +4596,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -4636,10 +4648,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -4656,10 +4668,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -4682,10 +4694,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -4708,10 +4720,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -4734,10 +4746,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -4760,10 +4772,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -4786,10 +4798,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -4812,10 +4824,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -4838,10 +4850,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -4864,10 +4876,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -4890,10 +4902,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -4916,10 +4928,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -4942,10 +4954,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4968,10 +4980,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4986,7 +4998,7 @@
         <v>-1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4994,10 +5006,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -5012,7 +5024,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5020,10 +5032,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -5038,7 +5050,7 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5046,10 +5058,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -5064,7 +5076,7 @@
         <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5072,10 +5084,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -5090,7 +5102,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5098,10 +5110,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -5116,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5124,10 +5136,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -5142,7 +5154,7 @@
         <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5150,10 +5162,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -5168,7 +5180,7 @@
         <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5176,10 +5188,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -5194,7 +5206,7 @@
         <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5202,10 +5214,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -5220,7 +5232,7 @@
         <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5228,10 +5240,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -5246,7 +5258,7 @@
         <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5254,10 +5266,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -5272,7 +5284,7 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5283,7 +5295,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -5307,7 +5319,7 @@
         <v>48</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5328,10 +5340,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -5352,10 +5364,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -5376,10 +5388,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -5400,10 +5412,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -5465,10 +5477,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -5485,10 +5497,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -5505,10 +5517,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -5525,10 +5537,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -5545,10 +5557,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -5565,10 +5577,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -5585,10 +5597,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -5602,10 +5614,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D9" s="1">
         <v>7</v>
@@ -5644,10 +5656,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -5661,10 +5673,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -5684,10 +5696,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -5707,10 +5719,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -5730,10 +5742,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -5753,10 +5765,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -5776,10 +5788,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -5799,10 +5811,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -5822,10 +5834,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -5845,10 +5857,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -5868,10 +5880,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -5891,10 +5903,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -5914,10 +5926,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -5937,10 +5949,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -5960,10 +5972,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -5983,10 +5995,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D16" s="1">
         <v>8</v>
@@ -6006,10 +6018,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D17" s="1">
         <v>8</v>
@@ -6029,10 +6041,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D18" s="1">
         <v>9</v>
@@ -6052,10 +6064,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D19" s="1">
         <v>9</v>
@@ -6075,10 +6087,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
@@ -6098,10 +6110,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D21" s="1">
         <v>10</v>
@@ -6121,10 +6133,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D22" s="1">
         <v>11</v>
@@ -6144,10 +6156,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D23" s="1">
         <v>11</v>
@@ -6167,10 +6179,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D24" s="1">
         <v>12</v>
@@ -6190,10 +6202,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D25" s="1">
         <v>12</v>
@@ -6213,10 +6225,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
@@ -6233,10 +6245,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -6253,10 +6265,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -6273,10 +6285,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -6286,6 +6298,64 @@
       </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6335,7 +6405,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>8</v>
@@ -6344,6 +6414,75 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -6399,7 +6538,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1">
-        <v>20</v>
+        <v>5000</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -6422,7 +6561,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="1">
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -6445,7 +6584,7 @@
         <v>19</v>
       </c>
       <c r="E4" s="1">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -6468,7 +6607,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -6491,7 +6630,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="1">
-        <v>30</v>
+        <v>5300</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -6514,7 +6653,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="1">
-        <v>30</v>
+        <v>3200</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -6537,7 +6676,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="1">
-        <v>40</v>
+        <v>2500</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -6560,7 +6699,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="1">
-        <v>40</v>
+        <v>3500</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -6808,7 +6947,7 @@
         <v>-160</v>
       </c>
       <c r="F2" s="1">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -6834,7 +6973,7 @@
         <v>160</v>
       </c>
       <c r="F3" s="1">
-        <v>50</v>
+        <v>3000</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -6860,7 +6999,7 @@
         <v>-20</v>
       </c>
       <c r="F4" s="1">
-        <v>70</v>
+        <v>2000</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -6886,7 +7025,7 @@
         <v>85</v>
       </c>
       <c r="F5" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -6912,7 +7051,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>30</v>
+        <v>5300</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -6938,7 +7077,7 @@
         <v>200</v>
       </c>
       <c r="F7" s="1">
-        <v>30</v>
+        <v>3200</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -6964,7 +7103,7 @@
         <v>-180</v>
       </c>
       <c r="F8" s="1">
-        <v>40</v>
+        <v>2500</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -6990,7 +7129,7 @@
         <v>180</v>
       </c>
       <c r="F9" s="1">
-        <v>40</v>
+        <v>3500</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -7016,7 +7155,7 @@
         <v>-161</v>
       </c>
       <c r="F10" s="1">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>32</v>
@@ -7039,7 +7178,7 @@
         <v>161</v>
       </c>
       <c r="F11" s="1">
-        <v>50</v>
+        <v>1500</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>32</v>
@@ -7062,7 +7201,7 @@
         <v>-21</v>
       </c>
       <c r="F12" s="1">
-        <v>50</v>
+        <v>5300</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>32</v>
@@ -7085,7 +7224,7 @@
         <v>86</v>
       </c>
       <c r="F13" s="1">
-        <v>50</v>
+        <v>3200</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>32</v>
@@ -7105,10 +7244,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F14" s="1">
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>32</v>
@@ -7131,7 +7270,7 @@
         <v>201</v>
       </c>
       <c r="F15" s="1">
-        <v>50</v>
+        <v>3500</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>32</v>
@@ -7154,7 +7293,7 @@
         <v>-181</v>
       </c>
       <c r="F16" s="1">
-        <v>50</v>
+        <v>2300</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>32</v>
@@ -7177,7 +7316,7 @@
         <v>181</v>
       </c>
       <c r="F17" s="1">
-        <v>50</v>
+        <v>4300</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>32</v>
@@ -7236,6 +7375,453 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.25" style="1" customWidth="1"/>
+    <col min="5" max="7" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:14">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:14">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:14">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:14">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:14">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:14">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:14">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A10" s="2">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A11" s="2">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A12" s="2">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A13" s="2">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A14" s="2">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A15" s="2">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:14">
+      <c r="A16" s="2">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A17" s="2">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5701</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H5"/>
@@ -7261,13 +7847,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -7281,10 +7867,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -7298,13 +7884,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -7324,13 +7910,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -7350,13 +7936,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -7368,450 +7954,6 @@
         <v>36</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.25" style="1" customWidth="1"/>
-    <col min="5" max="7" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="1">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:7">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="1">
-        <v>50</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="1">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="1">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="1">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="1">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="1">
-        <v>40</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="1">
-        <v>40</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A10" s="2">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A11" s="2">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A12" s="2">
-        <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A13" s="2">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A14" s="2">
-        <v>29</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A15" s="2">
-        <v>30</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A16" s="2">
-        <v>31</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
-      <c r="A17" s="2">
-        <v>32</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="1">
-        <v>5701</v>
-      </c>
-      <c r="G17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -7847,7 +7989,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -7861,13 +8003,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -7878,13 +8020,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -7895,13 +8037,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -7912,13 +8054,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -7929,13 +8071,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -7946,13 +8088,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -7963,16 +8105,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
@@ -8010,10 +8152,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -8030,10 +8172,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -8056,10 +8198,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -8082,10 +8224,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -8108,10 +8250,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -8134,10 +8276,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -8160,10 +8302,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -8186,10 +8328,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -8212,10 +8354,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -8238,10 +8380,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -8264,10 +8406,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -8290,10 +8432,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -8316,10 +8458,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -8342,10 +8484,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -8360,7 +8502,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8368,10 +8510,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -8386,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8394,10 +8536,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -8412,7 +8554,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8420,10 +8562,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -8438,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8446,10 +8588,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -8464,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8472,10 +8614,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -8490,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8498,10 +8640,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -8516,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8524,10 +8666,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" s="1">
         <v>4</v>
@@ -8542,7 +8684,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8550,10 +8692,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
@@ -8568,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8576,10 +8718,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
@@ -8594,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8602,10 +8744,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1">
         <v>6</v>
@@ -8620,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -8628,10 +8770,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
@@ -8646,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
@@ -8654,10 +8796,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -8674,10 +8816,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -8694,10 +8836,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -8714,10 +8856,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -8734,10 +8876,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -8754,10 +8896,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -8774,10 +8916,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -8797,10 +8939,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>

--- a/test_data/UltraArm_P1.xlsx
+++ b/test_data/UltraArm_P1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="14" activeTab="19"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -13,17 +13,17 @@
     <sheet name="set_angle" sheetId="21" r:id="rId4"/>
     <sheet name="get_angles_info" sheetId="18" r:id="rId5"/>
     <sheet name="set_coords" sheetId="23" r:id="rId6"/>
-    <sheet name="get_error_information" sheetId="11" r:id="rId7"/>
-    <sheet name="get_coords" sheetId="22" r:id="rId8"/>
-    <sheet name="send_coord" sheetId="24" r:id="rId9"/>
+    <sheet name="set_coord" sheetId="24" r:id="rId7"/>
+    <sheet name="get_error_information" sheetId="11" r:id="rId8"/>
+    <sheet name="get_coords_info" sheetId="22" r:id="rId9"/>
     <sheet name="set_jog_angle" sheetId="31" r:id="rId10"/>
     <sheet name="stop" sheetId="28" r:id="rId11"/>
     <sheet name="is_moving" sheetId="30" r:id="rId12"/>
     <sheet name="jog_rpy" sheetId="32" r:id="rId13"/>
-    <sheet name="jog_coord" sheetId="33" r:id="rId14"/>
+    <sheet name="set_jog_coord" sheetId="33" r:id="rId14"/>
     <sheet name="jog_increment_angle" sheetId="34" r:id="rId15"/>
     <sheet name="jog_increment_coord" sheetId="35" r:id="rId16"/>
-    <sheet name="set_servo_calibration" sheetId="45" r:id="rId17"/>
+    <sheet name="set_zero_calibration" sheetId="45" r:id="rId17"/>
     <sheet name="set_base_io_output" sheetId="52" r:id="rId18"/>
     <sheet name="set_joint_enable" sheetId="53" r:id="rId19"/>
     <sheet name="set_joint_release" sheetId="54" r:id="rId20"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="252">
   <si>
     <t>ID</t>
   </si>
@@ -97,6 +97,9 @@
     <t>[-160,0,90,0]</t>
   </si>
   <si>
+    <t>ok</t>
+  </si>
+  <si>
     <t>使一关节运动到正限位</t>
   </si>
   <si>
@@ -106,72 +109,75 @@
     <t>使二关节运动到负限位</t>
   </si>
   <si>
+    <t>[0,-20,110,0]</t>
+  </si>
+  <si>
+    <t>使二关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,85,90,0]</t>
+  </si>
+  <si>
+    <t>使三关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,90,0]</t>
+  </si>
+  <si>
+    <t>使三关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,50,200,0]</t>
+  </si>
+  <si>
+    <t>使四关节运动到负限位</t>
+  </si>
+  <si>
+    <t>[0,0,90,180]</t>
+  </si>
+  <si>
+    <t>使四关节运动到正限位</t>
+  </si>
+  <si>
+    <t>[0,0,90,-180]</t>
+  </si>
+  <si>
+    <t>全关节运动，角度超限</t>
+  </si>
+  <si>
+    <t>[-161,0,90,0]</t>
+  </si>
+  <si>
+    <t>exception</t>
+  </si>
+  <si>
+    <t>[161,0,90,0]</t>
+  </si>
+  <si>
+    <t>[0,-21,90,0]</t>
+  </si>
+  <si>
+    <t>[0,86,90,0]</t>
+  </si>
+  <si>
+    <t>[0,0,91,0]</t>
+  </si>
+  <si>
+    <t>[0,0,201,0]</t>
+  </si>
+  <si>
+    <t>[0,0,90,181]</t>
+  </si>
+  <si>
+    <t>[0,0,90,-181]</t>
+  </si>
+  <si>
+    <t>全关节运动，速度超限</t>
+  </si>
+  <si>
     <t>[0,-20,90,0]</t>
   </si>
   <si>
-    <t>使二关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[0,85,90,0]</t>
-  </si>
-  <si>
-    <t>使三关节运动到负限位</t>
-  </si>
-  <si>
-    <t>[0,0,90,0]</t>
-  </si>
-  <si>
-    <t>使三关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[0,0,200,0]</t>
-  </si>
-  <si>
-    <t>使四关节运动到负限位</t>
-  </si>
-  <si>
-    <t>[0,0,90,180]</t>
-  </si>
-  <si>
-    <t>使四关节运动到正限位</t>
-  </si>
-  <si>
-    <t>[0,0,90,-180]</t>
-  </si>
-  <si>
-    <t>全关节运动，角度超限</t>
-  </si>
-  <si>
-    <t>[-161,0,90,0]</t>
-  </si>
-  <si>
-    <t>exception</t>
-  </si>
-  <si>
-    <t>[161,0,90,0]</t>
-  </si>
-  <si>
-    <t>[0,-21,90,0]</t>
-  </si>
-  <si>
-    <t>[0,86,90,0]</t>
-  </si>
-  <si>
-    <t>[0,0,91,0]</t>
-  </si>
-  <si>
-    <t>[0,0,201,0]</t>
-  </si>
-  <si>
-    <t>[0,0,90,181]</t>
-  </si>
-  <si>
-    <t>[0,0,90,-181]</t>
-  </si>
-  <si>
-    <t>全关节运动，速度超限</t>
-  </si>
-  <si>
     <t>joint</t>
   </si>
   <si>
@@ -220,84 +226,123 @@
     <t>send_coords</t>
   </si>
   <si>
-    <t>[100,0.00,231.00,0.00]</t>
+    <t>[250, 0.07, 46.07, 0.0]</t>
   </si>
   <si>
     <t>运动x轴（反向）</t>
   </si>
   <si>
-    <t>[60,0.00,231.00,0.00]</t>
+    <t>[180, 0.07, 46.07, 0.0]</t>
   </si>
   <si>
     <t>运动y轴（正向）</t>
   </si>
   <si>
-    <t>[83.50,30,231.00,0.00]</t>
+    <t>[216.09, 50, 46.07, 0.0]</t>
   </si>
   <si>
     <t>运动y轴（反向）</t>
   </si>
   <si>
-    <t>[83.50,-30,231.00,0.00]</t>
+    <t>[216.09, -50, 46.07, 0.0]</t>
   </si>
   <si>
     <t>运动z轴（正向）</t>
   </si>
   <si>
-    <t>[83.50,0.00,200,0.00]</t>
+    <t>[216.09, 0.07, 90, 0.0]</t>
   </si>
   <si>
     <t>运动z轴（反向）</t>
   </si>
   <si>
-    <t>[83.50,0.00,240,0.00]</t>
+    <t>[216.09, 0.07, 0, 0.0]</t>
   </si>
   <si>
     <t>运动rx轴（正向）</t>
   </si>
   <si>
-    <t>[83.50,0.00,231.00,30]</t>
+    <t>[216.09, 0.07, 46.07, 30]</t>
   </si>
   <si>
     <t>运动rx轴（反向）</t>
   </si>
   <si>
+    <t>[216.09, 0.07, 46.07,-30]</t>
+  </si>
+  <si>
+    <t>全关节运动，坐标超限，x轴</t>
+  </si>
+  <si>
+    <t>[-303,0.00,231.00,-30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>[364,0.00,231.00,-30]</t>
+  </si>
+  <si>
+    <t>全关节运动，坐标超限，Y轴</t>
+  </si>
+  <si>
+    <t>[83.50,364,231.00,-30]</t>
+  </si>
+  <si>
+    <t>[83.50,-364,231.00,-30]</t>
+  </si>
+  <si>
+    <t>全关节运动，坐标超限，Z轴</t>
+  </si>
+  <si>
+    <t>[83.50,0.00,-158,-30]</t>
+  </si>
+  <si>
     <t>[83.50,0.00,231.00,-30]</t>
   </si>
   <si>
-    <t>全关节运动，坐标超限，x轴</t>
-  </si>
-  <si>
-    <t>[303,0.00,231.00,-30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>[364,0.00,231.00,-30]</t>
-  </si>
-  <si>
-    <t>全关节运动，坐标超限，Y轴</t>
-  </si>
-  <si>
-    <t>[83.50,364,231.00,-30]</t>
-  </si>
-  <si>
-    <t>[83.50,-364,231.00,-30]</t>
-  </si>
-  <si>
-    <t>全关节运动，坐标超限，Z轴</t>
-  </si>
-  <si>
-    <t>[83.50,0.00,-158,-30]</t>
+    <t>axis</t>
+  </si>
+  <si>
+    <t>coord</t>
+  </si>
+  <si>
+    <t>send_coord</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>运动r轴（正向）</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>运动r轴（反向）</t>
+  </si>
+  <si>
+    <t>坐标超限，x轴</t>
+  </si>
+  <si>
+    <t>坐标超限，Y轴</t>
+  </si>
+  <si>
+    <t>坐标超限，Z轴</t>
+  </si>
+  <si>
+    <t>速度超限</t>
   </si>
   <si>
     <t>target_angles</t>
   </si>
   <si>
-    <t>axis</t>
-  </si>
-  <si>
     <t>target_coord</t>
   </si>
   <si>
@@ -358,135 +403,45 @@
     <t>[111.0, -86.8, 360.6, -160.0, 0.0, -90.0]</t>
   </si>
   <si>
-    <t>coord</t>
-  </si>
-  <si>
-    <t>插补模式下，运动x轴（正向）</t>
-  </si>
-  <si>
-    <t>send_coord</t>
-  </si>
-  <si>
-    <t>插补模式下，运动x轴（反向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动y轴（正向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动y轴（反向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动z轴（正向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动z轴（反向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动rx轴（正向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动rx轴（反向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动ry轴（正向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动ry轴（反向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动rz轴（正向）</t>
-  </si>
-  <si>
-    <t>插补模式下，运动rz轴（反向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动x轴（正向）</t>
+    <t>position</t>
+  </si>
+  <si>
+    <t>target_angle</t>
+  </si>
+  <si>
+    <t>set_jog_angle</t>
+  </si>
+  <si>
+    <t>设置关节超限</t>
+  </si>
+  <si>
+    <t>设置方向超限</t>
+  </si>
+  <si>
+    <t>停止运动</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>停止运动（缓停）</t>
+  </si>
+  <si>
+    <t>输入参数超限</t>
+  </si>
+  <si>
+    <t>静止状态下查询运动状态</t>
+  </si>
+  <si>
+    <t>is_moving</t>
+  </si>
+  <si>
+    <t>运动状态下查询运动状态</t>
   </si>
   <si>
     <t>normal1</t>
   </si>
   <si>
-    <t>刷新模式下，运动x轴（反向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动y轴（正向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动y轴（反向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动z轴（正向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动z轴（反向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动rx轴（正向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动rx轴（反向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动ry轴（正向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动ry轴（反向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动rz轴（正向）</t>
-  </si>
-  <si>
-    <t>刷新模式下，运动rz轴（反向）</t>
-  </si>
-  <si>
-    <t>坐标超限，x轴</t>
-  </si>
-  <si>
-    <t>坐标超限，Y轴</t>
-  </si>
-  <si>
-    <t>坐标超限，Z轴</t>
-  </si>
-  <si>
-    <t>速度超限</t>
-  </si>
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>target_angle</t>
-  </si>
-  <si>
-    <t>set_jog_angle</t>
-  </si>
-  <si>
-    <t>设置关节超限</t>
-  </si>
-  <si>
-    <t>设置方向超限</t>
-  </si>
-  <si>
-    <t>停止运动</t>
-  </si>
-  <si>
-    <t>stop</t>
-  </si>
-  <si>
-    <t>停止运动（缓停）</t>
-  </si>
-  <si>
-    <t>输入参数超限</t>
-  </si>
-  <si>
-    <t>静止状态下查询运动状态</t>
-  </si>
-  <si>
-    <t>is_moving</t>
-  </si>
-  <si>
-    <t>运动状态下查询运动状态</t>
-  </si>
-  <si>
     <t>插补模式下，x轴进行rpy运动（负向）</t>
   </si>
   <si>
@@ -769,12 +724,15 @@
     <t>设置x轴增量超限</t>
   </si>
   <si>
+    <t>设置全关节零位</t>
+  </si>
+  <si>
+    <t>set_zero_calibration</t>
+  </si>
+  <si>
     <t>设置一关节零位</t>
   </si>
   <si>
-    <t>set_servo_calibration</t>
-  </si>
-  <si>
     <t>设置二关节零位</t>
   </si>
   <si>
@@ -782,12 +740,6 @@
   </si>
   <si>
     <t>设置四关节零位</t>
-  </si>
-  <si>
-    <t>设置五关节零位</t>
-  </si>
-  <si>
-    <t>设置六关节零位</t>
   </si>
   <si>
     <t>pin_no</t>
@@ -1879,13 +1831,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -1905,7 +1857,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -1919,8 +1871,8 @@
       <c r="G2" s="2">
         <v>3000</v>
       </c>
-      <c r="H2" s="2">
-        <v>1</v>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
@@ -1931,10 +1883,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -1948,8 +1900,8 @@
       <c r="G3" s="2">
         <v>2000</v>
       </c>
-      <c r="H3" s="2">
-        <v>1</v>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
@@ -1960,10 +1912,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -1977,8 +1929,8 @@
       <c r="G4" s="2">
         <v>1000</v>
       </c>
-      <c r="H4" s="2">
-        <v>1</v>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
@@ -1989,10 +1941,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -2006,8 +1958,8 @@
       <c r="G5" s="2">
         <v>4000</v>
       </c>
-      <c r="H5" s="2">
-        <v>1</v>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
@@ -2018,10 +1970,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -2035,8 +1987,8 @@
       <c r="G6" s="2">
         <v>5000</v>
       </c>
-      <c r="H6" s="2">
-        <v>1</v>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
@@ -2047,10 +1999,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -2064,8 +2016,8 @@
       <c r="G7" s="2">
         <v>4000</v>
       </c>
-      <c r="H7" s="2">
-        <v>1</v>
+      <c r="H7" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
@@ -2076,10 +2028,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -2093,8 +2045,8 @@
       <c r="G8" s="2">
         <v>5000</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
+      <c r="H8" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
@@ -2105,10 +2057,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -2122,8 +2074,8 @@
       <c r="G9" s="2">
         <v>2000</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
+      <c r="H9" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
@@ -2134,10 +2086,10 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -2153,7 +2105,7 @@
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:9">
@@ -2161,10 +2113,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D11" s="2">
         <v>4</v>
@@ -2180,7 +2132,7 @@
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2188,10 +2140,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2206,7 +2158,7 @@
         <v>3000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2214,10 +2166,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -2232,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2240,10 +2192,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -2258,7 +2210,7 @@
         <v>2000</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2266,10 +2218,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -2284,7 +2236,7 @@
         <v>1000</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2319,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -2333,10 +2285,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -2353,10 +2305,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -2373,16 +2325,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
@@ -2390,16 +2342,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2434,7 +2386,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -2448,10 +2400,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
@@ -2466,17 +2418,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2512,10 +2464,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -2532,10 +2484,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2558,10 +2510,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -2584,10 +2536,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -2610,10 +2562,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -2636,10 +2588,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -2662,10 +2614,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -2688,10 +2640,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -2706,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2714,10 +2666,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -2732,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2740,10 +2692,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -2758,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2766,10 +2718,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -2784,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2792,10 +2744,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -2810,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -2818,10 +2770,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -2836,7 +2788,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
@@ -2844,10 +2796,10 @@
         <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -2860,7 +2812,7 @@
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
@@ -2868,10 +2820,10 @@
         <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D15" s="2">
         <v>4</v>
@@ -2884,7 +2836,7 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
@@ -2892,10 +2844,10 @@
         <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -2908,7 +2860,7 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:8">
@@ -2916,10 +2868,10 @@
         <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -2932,7 +2884,7 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:8">
@@ -2940,10 +2892,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -2956,7 +2908,7 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:8">
@@ -2964,10 +2916,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2">
         <v>4</v>
@@ -2980,7 +2932,7 @@
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3016,10 +2968,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -3036,10 +2988,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3062,10 +3014,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3088,10 +3040,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -3114,10 +3066,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -3140,10 +3092,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -3158,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3166,10 +3118,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -3192,10 +3144,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -3218,10 +3170,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -3244,10 +3196,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -3270,10 +3222,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -3296,10 +3248,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -3322,10 +3274,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -3348,10 +3300,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -3366,7 +3318,7 @@
         <v>-1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3374,10 +3326,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -3392,7 +3344,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3400,10 +3352,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -3418,7 +3370,7 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3426,10 +3378,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -3444,7 +3396,7 @@
         <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3452,10 +3404,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -3470,7 +3422,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -3478,10 +3430,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -3496,7 +3448,7 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3504,10 +3456,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -3522,7 +3474,7 @@
         <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3530,10 +3482,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -3548,7 +3500,7 @@
         <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3556,10 +3508,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -3574,7 +3526,7 @@
         <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3582,10 +3534,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -3600,7 +3552,7 @@
         <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3608,10 +3560,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -3626,7 +3578,7 @@
         <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -3634,10 +3586,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -3652,7 +3604,7 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:8">
@@ -3660,10 +3612,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -3676,7 +3628,7 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:8">
@@ -3684,10 +3636,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -3700,7 +3652,7 @@
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:8">
@@ -3708,10 +3660,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -3724,7 +3676,7 @@
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
@@ -3732,10 +3684,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -3748,7 +3700,7 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:8">
@@ -3756,10 +3708,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -3772,7 +3724,7 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
@@ -3780,10 +3732,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D31" s="2">
         <v>4</v>
@@ -3796,7 +3748,7 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3832,10 +3784,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -3852,10 +3804,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3878,10 +3830,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3904,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -3930,10 +3882,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -3956,10 +3908,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -3982,10 +3934,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -4008,10 +3960,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -4034,10 +3986,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -4060,10 +4012,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -4086,10 +4038,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -4112,10 +4064,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -4138,10 +4090,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4164,10 +4116,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4182,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4190,10 +4142,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -4208,7 +4160,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4216,10 +4168,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -4234,7 +4186,7 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4242,10 +4194,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -4260,7 +4212,7 @@
         <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4268,10 +4220,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -4286,7 +4238,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4294,10 +4246,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -4312,7 +4264,7 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4320,10 +4272,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -4338,7 +4290,7 @@
         <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4346,10 +4298,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -4364,7 +4316,7 @@
         <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4372,10 +4324,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -4390,7 +4342,7 @@
         <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4398,10 +4350,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -4416,7 +4368,7 @@
         <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4424,10 +4376,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -4442,7 +4394,7 @@
         <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
@@ -4450,10 +4402,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -4468,7 +4420,7 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4476,10 +4428,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -4492,7 +4444,7 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4500,10 +4452,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -4516,7 +4468,7 @@
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4524,10 +4476,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -4540,7 +4492,7 @@
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4548,10 +4500,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -4564,7 +4516,7 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4572,10 +4524,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -4588,7 +4540,7 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -4596,10 +4548,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -4612,7 +4564,7 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4648,10 +4600,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>12</v>
@@ -4668,10 +4620,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -4694,10 +4646,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -4720,10 +4672,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -4746,10 +4698,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -4772,10 +4724,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -4798,10 +4750,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -4824,10 +4776,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -4850,10 +4802,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -4876,10 +4828,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -4902,10 +4854,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -4928,10 +4880,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -4954,10 +4906,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4980,10 +4932,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4998,7 +4950,7 @@
         <v>-1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5006,10 +4958,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -5024,7 +4976,7 @@
         <v>-1</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5032,10 +4984,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -5050,7 +5002,7 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5058,10 +5010,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -5076,7 +5028,7 @@
         <v>-1</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5084,10 +5036,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -5102,7 +5054,7 @@
         <v>-1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5110,10 +5062,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -5128,7 +5080,7 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5136,10 +5088,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -5154,7 +5106,7 @@
         <v>-1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5162,10 +5114,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D21" s="2">
         <v>4</v>
@@ -5180,7 +5132,7 @@
         <v>-1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5188,10 +5140,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D22" s="2">
         <v>5</v>
@@ -5206,7 +5158,7 @@
         <v>-1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5214,10 +5166,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -5232,7 +5184,7 @@
         <v>-1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5240,10 +5192,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -5258,7 +5210,7 @@
         <v>-1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5266,10 +5218,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -5284,7 +5236,7 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5292,10 +5244,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -5308,7 +5260,7 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5316,10 +5268,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5332,7 +5284,7 @@
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5340,10 +5292,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -5356,7 +5308,7 @@
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5364,10 +5316,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D29" s="2">
         <v>7</v>
@@ -5380,7 +5332,7 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5388,10 +5340,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -5404,7 +5356,7 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -5412,10 +5364,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -5428,7 +5380,7 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -5440,8 +5392,8 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
@@ -5463,7 +5415,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -5472,60 +5424,58 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
+    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
       <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="33" customHeight="1" spans="1:6">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="B4" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D4" s="1">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -5534,18 +5484,18 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D5" s="1">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -5554,18 +5504,18 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -5574,56 +5524,36 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D7" s="1">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D9" s="1">
-        <v>7</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -5656,10 +5586,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -5673,10 +5603,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -5696,10 +5626,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -5719,10 +5649,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
@@ -5742,10 +5672,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -5765,10 +5695,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -5788,10 +5718,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -5811,10 +5741,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -5834,10 +5764,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -5857,10 +5787,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -5880,10 +5810,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -5903,10 +5833,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D12" s="1">
         <v>6</v>
@@ -5926,10 +5856,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -5949,10 +5879,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D14" s="1">
         <v>7</v>
@@ -5972,10 +5902,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D15" s="1">
         <v>7</v>
@@ -5995,10 +5925,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D16" s="1">
         <v>8</v>
@@ -6018,10 +5948,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D17" s="1">
         <v>8</v>
@@ -6041,10 +5971,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D18" s="1">
         <v>9</v>
@@ -6064,10 +5994,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D19" s="1">
         <v>9</v>
@@ -6087,10 +6017,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D20" s="1">
         <v>10</v>
@@ -6110,10 +6040,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D21" s="1">
         <v>10</v>
@@ -6133,10 +6063,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D22" s="1">
         <v>11</v>
@@ -6156,10 +6086,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D23" s="1">
         <v>11</v>
@@ -6179,10 +6109,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D24" s="1">
         <v>12</v>
@@ -6202,10 +6132,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D25" s="1">
         <v>12</v>
@@ -6225,10 +6155,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D26" s="1">
         <v>13</v>
@@ -6237,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6245,10 +6175,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -6257,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -6265,10 +6195,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -6277,7 +6207,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6285,10 +6215,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -6297,7 +6227,7 @@
         <v>-1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6332,7 +6262,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -6346,10 +6276,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -6444,7 +6374,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -6458,10 +6388,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -6540,8 +6470,8 @@
       <c r="E2" s="1">
         <v>5000</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -6552,19 +6482,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1">
         <v>3000</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
@@ -6575,19 +6505,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1">
         <v>2000</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
@@ -6598,19 +6528,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>1000</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
@@ -6621,19 +6551,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1">
         <v>5300</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -6644,19 +6574,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>3200</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>8</v>
@@ -6667,19 +6597,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1">
         <v>2500</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>8</v>
@@ -6690,19 +6620,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
         <v>3500</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
+      <c r="F9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>8</v>
@@ -6713,16 +6643,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="1:7">
@@ -6730,16 +6660,16 @@
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:7">
@@ -6747,16 +6677,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:7">
@@ -6764,16 +6694,16 @@
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="28.8" spans="1:7">
@@ -6781,16 +6711,16 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="28.8" spans="1:7">
@@ -6798,16 +6728,16 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:7">
@@ -6815,16 +6745,16 @@
         <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="28.8" spans="1:7">
@@ -6832,16 +6762,16 @@
         <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="28.8" spans="1:7">
@@ -6849,19 +6779,19 @@
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="28.8" spans="1:7">
@@ -6869,19 +6799,19 @@
         <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1">
         <v>5701</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6915,10 +6845,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -6938,19 +6868,19 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>-160</v>
+        <v>-158</v>
       </c>
       <c r="F2" s="1">
         <v>5000</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -6961,22 +6891,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3" s="1">
         <v>3000</v>
       </c>
-      <c r="G3" s="1">
-        <v>0</v>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>8</v>
@@ -6987,22 +6917,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="F4" s="1">
         <v>2000</v>
       </c>
-      <c r="G4" s="1">
-        <v>0</v>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>8</v>
@@ -7013,22 +6943,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1">
         <v>1000</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
@@ -7039,22 +6969,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" s="1">
         <v>5300</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
+      <c r="G6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>8</v>
@@ -7065,22 +6995,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F7" s="1">
         <v>3200</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>8</v>
@@ -7091,10 +7021,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -7105,8 +7035,8 @@
       <c r="F8" s="1">
         <v>2500</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>8</v>
@@ -7117,10 +7047,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
@@ -7131,8 +7061,8 @@
       <c r="F9" s="1">
         <v>3500</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>8</v>
@@ -7143,10 +7073,10 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -7158,7 +7088,7 @@
         <v>1000</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7166,10 +7096,10 @@
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -7181,7 +7111,7 @@
         <v>1500</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7189,10 +7119,10 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -7204,7 +7134,7 @@
         <v>5300</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7212,10 +7142,10 @@
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -7227,7 +7157,7 @@
         <v>3200</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7235,10 +7165,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -7250,7 +7180,7 @@
         <v>2500</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7258,10 +7188,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -7273,7 +7203,7 @@
         <v>3500</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7281,10 +7211,10 @@
         <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16" s="1">
         <v>4</v>
@@ -7296,7 +7226,7 @@
         <v>2300</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -7304,10 +7234,10 @@
         <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -7319,7 +7249,7 @@
         <v>4300</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:8">
@@ -7327,10 +7257,10 @@
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -7342,7 +7272,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:8">
@@ -7350,10 +7280,10 @@
         <v>38</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
@@ -7365,7 +7295,7 @@
         <v>5701</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -7400,7 +7330,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -7414,13 +7344,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -7431,13 +7361,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -7474,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>12</v>
@@ -7491,19 +7421,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1">
         <v>5000</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -7514,19 +7444,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E3" s="1">
         <v>3000</v>
       </c>
-      <c r="F3" s="1">
-        <v>0</v>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
@@ -7537,19 +7467,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E4" s="1">
         <v>2000</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
@@ -7560,19 +7490,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1">
         <v>1000</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
@@ -7583,19 +7513,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1">
         <v>5000</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -7606,19 +7536,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" s="1">
         <v>3000</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>8</v>
@@ -7629,19 +7559,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1">
         <v>2000</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>8</v>
@@ -7652,19 +7582,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1">
         <v>1000</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
+      <c r="F9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>8</v>
@@ -7675,19 +7605,19 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:14">
@@ -7695,16 +7625,16 @@
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:14">
@@ -7712,16 +7642,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:14">
@@ -7729,16 +7659,16 @@
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:14">
@@ -7746,16 +7676,16 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:14">
@@ -7763,16 +7693,16 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:14">
@@ -7780,19 +7710,19 @@
         <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
@@ -7800,19 +7730,19 @@
         <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1">
         <v>5701</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -7822,6 +7752,454 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.6296296296296" style="2" customWidth="1"/>
+    <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="2">
+        <v>250</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="2">
+        <v>180</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-50</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="2">
+        <v>90</v>
+      </c>
+      <c r="F8" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-90</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A10" s="2">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-303</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4001</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A11" s="2">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>364</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4002</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A12" s="2">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>364</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4003</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A13" s="2">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-364</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4004</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A14" s="2">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>91</v>
+      </c>
+      <c r="F14" s="2">
+        <v>4005</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A15" s="2">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>201</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4006</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A16" s="2">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>90</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
+      <c r="A17" s="2">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="2">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>90</v>
+      </c>
+      <c r="F17" s="2">
+        <v>5701</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H5"/>
@@ -7847,13 +8225,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -7867,10 +8245,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -7884,13 +8262,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -7902,7 +8280,7 @@
         <v>36</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="43.2" spans="1:8">
@@ -7910,13 +8288,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -7928,7 +8306,7 @@
         <v>36</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="43.2" spans="1:8">
@@ -7936,13 +8314,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -7954,7 +8332,7 @@
         <v>36</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -7963,7 +8341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F8"/>
@@ -7989,7 +8367,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -8003,13 +8381,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -8020,13 +8398,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -8037,13 +8415,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -8054,13 +8432,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -8071,13 +8449,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -8088,13 +8466,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -8105,856 +8483,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1296296296296" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.6296296296296" style="1" customWidth="1"/>
-    <col min="6" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>200</v>
-      </c>
-      <c r="F2" s="1">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="33" customHeight="1" spans="1:8">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1">
-        <v>100</v>
-      </c>
-      <c r="F3" s="1">
-        <v>50</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>-30</v>
-      </c>
-      <c r="F4" s="1">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>-150</v>
-      </c>
-      <c r="F5" s="1">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="1">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>350</v>
-      </c>
-      <c r="F6" s="1">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1">
-        <v>250</v>
-      </c>
-      <c r="F7" s="1">
-        <v>30</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1">
-        <v>-160</v>
-      </c>
-      <c r="F8" s="1">
-        <v>40</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="1">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1">
-        <v>150</v>
-      </c>
-      <c r="F9" s="1">
-        <v>40</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1">
-        <v>50</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="1">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1">
-        <v>-30</v>
-      </c>
-      <c r="F11" s="1">
-        <v>50</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="1">
-        <v>6</v>
-      </c>
-      <c r="E12" s="1">
-        <v>-40</v>
-      </c>
-      <c r="F12" s="1">
-        <v>60</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="1">
-        <v>6</v>
-      </c>
-      <c r="E13" s="1">
-        <v>-14</v>
-      </c>
-      <c r="F13" s="1">
-        <v>60</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>200</v>
-      </c>
-      <c r="F14" s="1">
-        <v>20</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>100</v>
-      </c>
-      <c r="F15" s="1">
-        <v>50</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <v>-30</v>
-      </c>
-      <c r="F16" s="1">
-        <v>20</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>-150</v>
-      </c>
-      <c r="F17" s="1">
-        <v>20</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1">
-        <v>350</v>
-      </c>
-      <c r="F18" s="1">
-        <v>30</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="1">
-        <v>3</v>
-      </c>
-      <c r="E19" s="1">
-        <v>250</v>
-      </c>
-      <c r="F19" s="1">
-        <v>30</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1">
-        <v>-160</v>
-      </c>
-      <c r="F20" s="1">
-        <v>40</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="1">
-        <v>4</v>
-      </c>
-      <c r="E21" s="1">
-        <v>150</v>
-      </c>
-      <c r="F21" s="1">
-        <v>40</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="1">
-        <v>5</v>
-      </c>
-      <c r="E22" s="1">
-        <v>30</v>
-      </c>
-      <c r="F22" s="1">
-        <v>50</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" s="1">
-        <v>5</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-30</v>
-      </c>
-      <c r="F23" s="1">
-        <v>50</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" s="1">
-        <v>6</v>
-      </c>
-      <c r="E24" s="1">
-        <v>-40</v>
-      </c>
-      <c r="F24" s="1">
-        <v>100</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="1">
-        <v>6</v>
-      </c>
-      <c r="E25" s="1">
-        <v>-14</v>
-      </c>
-      <c r="F25" s="1">
-        <v>100</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
-        <v>-467</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
-        <v>467</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1">
-        <v>-467</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1">
-        <v>467</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1">
-        <v>-151</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1">
-        <v>678</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>350</v>
-      </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="26" customHeight="1" spans="1:8">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="1">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1">
-        <v>250</v>
-      </c>
-      <c r="F33" s="1">
-        <v>101</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/UltraArm_P1.xlsx
+++ b/test_data/UltraArm_P1.xlsx
@@ -4,30 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="10500" firstSheet="17" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
-    <sheet name="get_modify_version" sheetId="3" r:id="rId2"/>
-    <sheet name="set_angles" sheetId="19" r:id="rId3"/>
-    <sheet name="set_angle" sheetId="21" r:id="rId4"/>
-    <sheet name="get_angles_info" sheetId="18" r:id="rId5"/>
-    <sheet name="set_coords" sheetId="23" r:id="rId6"/>
-    <sheet name="set_coord" sheetId="24" r:id="rId7"/>
-    <sheet name="get_error_information" sheetId="11" r:id="rId8"/>
-    <sheet name="get_coords_info" sheetId="22" r:id="rId9"/>
-    <sheet name="set_jog_angle" sheetId="31" r:id="rId10"/>
-    <sheet name="stop" sheetId="28" r:id="rId11"/>
-    <sheet name="is_moving" sheetId="30" r:id="rId12"/>
-    <sheet name="jog_rpy" sheetId="32" r:id="rId13"/>
-    <sheet name="set_jog_coord" sheetId="33" r:id="rId14"/>
-    <sheet name="jog_increment_angle" sheetId="34" r:id="rId15"/>
-    <sheet name="jog_increment_coord" sheetId="35" r:id="rId16"/>
-    <sheet name="set_zero_calibration" sheetId="45" r:id="rId17"/>
-    <sheet name="set_base_io_output" sheetId="52" r:id="rId18"/>
-    <sheet name="set_joint_enable" sheetId="53" r:id="rId19"/>
-    <sheet name="set_joint_release" sheetId="54" r:id="rId20"/>
-    <sheet name="Sheet3" sheetId="55" r:id="rId21"/>
+    <sheet name="get_modify_version" sheetId="2" r:id="rId2"/>
+    <sheet name="set_angles" sheetId="3" r:id="rId3"/>
+    <sheet name="set_angle" sheetId="4" r:id="rId4"/>
+    <sheet name="get_angles_info" sheetId="5" r:id="rId5"/>
+    <sheet name="set_coords" sheetId="6" r:id="rId6"/>
+    <sheet name="set_coord" sheetId="7" r:id="rId7"/>
+    <sheet name="get_error_information" sheetId="8" r:id="rId8"/>
+    <sheet name="get_coords_info" sheetId="9" r:id="rId9"/>
+    <sheet name="set_jog_angle" sheetId="10" r:id="rId10"/>
+    <sheet name="stop" sheetId="11" r:id="rId11"/>
+    <sheet name="is_moving" sheetId="12" r:id="rId12"/>
+    <sheet name="jog_rpy" sheetId="13" r:id="rId13"/>
+    <sheet name="set_jog_coord" sheetId="14" r:id="rId14"/>
+    <sheet name="jog_increment_angle" sheetId="15" r:id="rId15"/>
+    <sheet name="jog_increment_coord" sheetId="16" r:id="rId16"/>
+    <sheet name="set_zero_calibration" sheetId="17" r:id="rId17"/>
+    <sheet name="set_base_io_output" sheetId="18" r:id="rId18"/>
+    <sheet name="set_joint_enable" sheetId="19" r:id="rId19"/>
+    <sheet name="set_joint_release" sheetId="20" r:id="rId20"/>
+    <sheet name="Sheet3" sheetId="21" r:id="rId21"/>
+    <sheet name="set_digital_io_output" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="259">
   <si>
     <t>ID</t>
   </si>
@@ -803,6 +804,27 @@
   </si>
   <si>
     <t>set_joint_release</t>
+  </si>
+  <si>
+    <t>引脚1高电平</t>
+  </si>
+  <si>
+    <t>set_digital_io_output</t>
+  </si>
+  <si>
+    <t>引脚1低电平</t>
+  </si>
+  <si>
+    <t>引脚2高电平</t>
+  </si>
+  <si>
+    <t>引脚2低电平</t>
+  </si>
+  <si>
+    <t>引脚号超限</t>
+  </si>
+  <si>
+    <t>状态非法</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1441,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1429,15 +1451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1755,7 +1769,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="6" width="18" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1774,25 +1788,25 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28.8" customHeight="1" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1817,7 +1831,7 @@
     <col min="6" max="6" width="28.5" style="2" customWidth="1"/>
     <col min="7" max="8" width="13.5555555555556" style="2" customWidth="1"/>
     <col min="9" max="9" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
@@ -1907,7 +1921,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:9">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1936,7 +1950,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:9">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1965,7 +1979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:9">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1994,7 +2008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:9">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2023,7 +2037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:9">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2052,7 +2066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:9">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2254,13 +2268,13 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2369,13 +2383,13 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2450,7 +2464,7 @@
     <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
     <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -2531,7 +2545,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2557,7 +2571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2583,7 +2597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2609,7 +2623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2635,7 +2649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A8" s="2">
         <v>13</v>
       </c>
@@ -2661,7 +2675,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A9" s="2">
         <v>14</v>
       </c>
@@ -2687,7 +2701,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A10" s="2">
         <v>15</v>
       </c>
@@ -2713,7 +2727,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A11" s="2">
         <v>16</v>
       </c>
@@ -2739,7 +2753,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A12" s="2">
         <v>17</v>
       </c>
@@ -2765,7 +2779,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A13" s="2">
         <v>18</v>
       </c>
@@ -2954,7 +2968,7 @@
     <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
     <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -3035,7 +3049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3061,7 +3075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3087,7 +3101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3113,7 +3127,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3139,7 +3153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3165,7 +3179,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3191,7 +3205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3217,7 +3231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -3243,7 +3257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3269,7 +3283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3295,7 +3309,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3321,7 +3335,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3347,7 +3361,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3373,7 +3387,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3399,7 +3413,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3425,7 +3439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3451,7 +3465,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3477,7 +3491,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3503,7 +3517,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3529,7 +3543,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3555,7 +3569,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3581,7 +3595,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3770,7 +3784,7 @@
     <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
     <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -3851,7 +3865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3877,7 +3891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3903,7 +3917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3929,7 +3943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3955,7 +3969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3981,7 +3995,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4007,7 +4021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4033,7 +4047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4059,7 +4073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4085,7 +4099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -4111,7 +4125,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4137,7 +4151,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4163,7 +4177,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4189,7 +4203,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4215,7 +4229,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4241,7 +4255,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4267,7 +4281,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4293,7 +4307,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4319,7 +4333,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4345,7 +4359,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4371,7 +4385,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4397,7 +4411,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="43.2" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="43.2" customHeight="1" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4423,7 +4437,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4447,7 +4461,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4471,7 +4485,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4495,7 +4509,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4519,7 +4533,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4543,7 +4557,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4586,7 +4600,7 @@
     <col min="5" max="5" width="21.6296296296296" style="2" customWidth="1"/>
     <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -4667,7 +4681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4719,7 +4733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4745,7 +4759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4771,7 +4785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4797,7 +4811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4823,7 +4837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4849,7 +4863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4875,7 +4889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4901,7 +4915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -4927,7 +4941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4953,7 +4967,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4979,7 +4993,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -5005,7 +5019,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -5031,7 +5045,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -5057,7 +5071,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -5083,7 +5097,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -5109,7 +5123,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -5135,7 +5149,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -5161,7 +5175,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="23" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -5187,7 +5201,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="24" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -5213,7 +5227,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="25" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -5239,7 +5253,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="26" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -5263,7 +5277,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="27" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -5287,7 +5301,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="28" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -5311,7 +5325,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="29" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -5335,7 +5349,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="30" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -5359,7 +5373,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="31" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -5398,10 +5412,10 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -5424,7 +5438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="2" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>225</v>
@@ -5482,7 +5496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -5502,7 +5516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="6" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -5522,7 +5536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="7" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -5539,7 +5553,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="8" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -5572,7 +5586,7 @@
     <col min="2" max="3" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="4" max="6" width="28.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
@@ -6245,13 +6259,13 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6300,7 +6314,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="6" width="18" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6319,25 +6333,25 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28.8" spans="1:6">
+    <row r="2" ht="28.8" customHeight="1" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -6357,13 +6371,13 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.8796296296296" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.6296296296296" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6417,6 +6431,183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="16.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="21.5555555555556" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6">
+        <v>99</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -6428,7 +6619,7 @@
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" customWidth="1"/>
     <col min="5" max="7" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
@@ -6500,7 +6691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:7">
+    <row r="4" ht="28.8" customHeight="1" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6523,7 +6714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:7">
+    <row r="5" ht="28.8" customHeight="1" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -6546,7 +6737,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:7">
+    <row r="6" ht="28.8" customHeight="1" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -6569,7 +6760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:7">
+    <row r="7" ht="28.8" customHeight="1" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -6592,7 +6783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:7">
+    <row r="8" ht="28.8" customHeight="1" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -6615,7 +6806,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:7">
+    <row r="9" ht="28.8" customHeight="1" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -6638,7 +6829,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:7">
+    <row r="10" ht="28.8" customHeight="1" spans="1:7">
       <c r="A10" s="2">
         <v>25</v>
       </c>
@@ -6655,7 +6846,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:7">
+    <row r="11" ht="28.8" customHeight="1" spans="1:7">
       <c r="A11" s="2">
         <v>26</v>
       </c>
@@ -6672,7 +6863,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:7">
+    <row r="12" ht="28.8" customHeight="1" spans="1:7">
       <c r="A12" s="2">
         <v>27</v>
       </c>
@@ -6689,7 +6880,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:7">
+    <row r="13" ht="28.8" customHeight="1" spans="1:7">
       <c r="A13" s="2">
         <v>28</v>
       </c>
@@ -6706,7 +6897,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:7">
+    <row r="14" ht="28.8" customHeight="1" spans="1:7">
       <c r="A14" s="2">
         <v>29</v>
       </c>
@@ -6723,7 +6914,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:7">
+    <row r="15" ht="28.8" customHeight="1" spans="1:7">
       <c r="A15" s="2">
         <v>30</v>
       </c>
@@ -6740,7 +6931,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:7">
+    <row r="16" ht="28.8" customHeight="1" spans="1:7">
       <c r="A16" s="2">
         <v>31</v>
       </c>
@@ -6757,7 +6948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:7">
+    <row r="17" ht="28.8" customHeight="1" spans="1:7">
       <c r="A17" s="2">
         <v>32</v>
       </c>
@@ -6774,7 +6965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:7">
+    <row r="18" ht="28.8" customHeight="1" spans="1:7">
       <c r="A18" s="2">
         <v>37</v>
       </c>
@@ -6794,7 +6985,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:7">
+    <row r="19" ht="28.8" customHeight="1" spans="1:7">
       <c r="A19" s="2">
         <v>38</v>
       </c>
@@ -6831,7 +7022,7 @@
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.5" style="1" customWidth="1"/>
     <col min="6" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -6912,7 +7103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="4" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6938,7 +7129,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="5" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -6964,7 +7155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="6" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -6990,7 +7181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="7" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -7016,7 +7207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7042,7 +7233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="9" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7068,7 +7259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="10" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A10" s="2">
         <v>25</v>
       </c>
@@ -7091,7 +7282,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="11" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A11" s="2">
         <v>26</v>
       </c>
@@ -7114,7 +7305,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="12" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A12" s="2">
         <v>27</v>
       </c>
@@ -7137,7 +7328,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="13" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A13" s="2">
         <v>28</v>
       </c>
@@ -7160,7 +7351,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="14" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A14" s="2">
         <v>29</v>
       </c>
@@ -7183,7 +7374,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="15" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A15" s="2">
         <v>30</v>
       </c>
@@ -7206,7 +7397,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="16" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A16" s="2">
         <v>31</v>
       </c>
@@ -7229,7 +7420,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A17" s="2">
         <v>32</v>
       </c>
@@ -7313,13 +7504,13 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+    <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7390,7 +7581,7 @@
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="48.25" style="1" customWidth="1"/>
     <col min="5" max="7" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:14">
@@ -7554,7 +7745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="8" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7577,7 +7768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="9" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7600,7 +7791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="10" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A10" s="2">
         <v>25</v>
       </c>
@@ -7620,7 +7811,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="11" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A11" s="2">
         <v>26</v>
       </c>
@@ -7637,7 +7828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="12" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A12" s="2">
         <v>27</v>
       </c>
@@ -7654,7 +7845,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="13" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A13" s="2">
         <v>28</v>
       </c>
@@ -7671,7 +7862,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="14" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A14" s="2">
         <v>29</v>
       </c>
@@ -7688,7 +7879,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="15" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A15" s="2">
         <v>30</v>
       </c>
@@ -7705,7 +7896,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:14">
+    <row r="16" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:14">
       <c r="A16" s="2">
         <v>31</v>
       </c>
@@ -7725,7 +7916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:7">
+    <row r="17" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:7">
       <c r="A17" s="2">
         <v>32</v>
       </c>
@@ -7764,7 +7955,7 @@
     <col min="5" max="5" width="19.6296296296296" style="2" customWidth="1"/>
     <col min="6" max="7" width="13.5555555555556" style="2" customWidth="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -8209,12 +8400,12 @@
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.6296296296296" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="1"/>
+    <col min="5" max="7" width="9" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8283,7 +8474,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" ht="43.2" spans="1:8">
+    <row r="4" ht="43.2" customHeight="1" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -8309,7 +8500,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="43.2" spans="1:8">
+    <row r="5" ht="43.2" customHeight="1" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -8353,7 +8544,7 @@
     <col min="4" max="4" width="20.3796296296296" style="1" customWidth="1"/>
     <col min="5" max="5" width="50" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8485,7 +8676,7 @@
       <c r="B8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D8" s="1" t="s">

--- a/test_data/UltraArm_P1.xlsx
+++ b/test_data/UltraArm_P1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="5" activeTab="5"/>
+    <workbookView windowWidth="25600" windowHeight="12080" firstSheet="6" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="413">
   <si>
     <t>ID</t>
   </si>
@@ -157,7 +157,7 @@
     <t>使二关节运动到负限位</t>
   </si>
   <si>
-    <t>[0,-18,110,0]</t>
+    <t>[0,-18,130,0]</t>
   </si>
   <si>
     <t>使二关节运动到正限位</t>
@@ -619,9 +619,15 @@
     <t>set_jog_coord</t>
   </si>
   <si>
+    <t>J2、J3 关节耦合</t>
+  </si>
+  <si>
     <t>使x轴运动到正限位</t>
   </si>
   <si>
+    <t>坐标无解</t>
+  </si>
+  <si>
     <t>使y轴运动到负限位</t>
   </si>
   <si>
@@ -629,6 +635,9 @@
   </si>
   <si>
     <t>使z轴运动到负限位</t>
+  </si>
+  <si>
+    <t>J2、J3耦合</t>
   </si>
   <si>
     <t>使z轴运动到正限位</t>
@@ -3459,7 +3468,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -3470,7 +3479,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>173</v>
@@ -3485,7 +3494,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -3496,7 +3505,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>173</v>
@@ -3511,7 +3520,7 @@
         <v>70</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -3522,7 +3531,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>173</v>
@@ -3534,10 +3543,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="3">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -3548,7 +3557,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>173</v>
@@ -3563,7 +3572,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -3574,7 +3583,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>173</v>
@@ -3589,7 +3598,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
@@ -3600,7 +3609,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>173</v>
@@ -3626,7 +3635,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>173</v>
@@ -3827,7 +3836,7 @@
         <v>44</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>12</v>
@@ -3847,10 +3856,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -3876,10 +3885,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -3905,10 +3914,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
@@ -3934,22 +3943,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="D5" s="3">
         <v>2</v>
       </c>
       <c r="E5" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3">
         <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -3963,22 +3972,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="3">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="F6" s="3">
         <v>30</v>
       </c>
       <c r="G6" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -3992,10 +4001,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -4021,10 +4030,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D8" s="3">
         <v>4</v>
@@ -4050,10 +4059,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D9" s="3">
         <v>4</v>
@@ -4082,7 +4091,7 @@
         <v>54</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -4107,7 +4116,7 @@
         <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D11" s="3">
         <v>4</v>
@@ -4132,7 +4141,7 @@
         <v>150</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -4157,7 +4166,7 @@
         <v>150</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D13" s="3">
         <v>5</v>
@@ -4179,10 +4188,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -4204,10 +4213,10 @@
         <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -4268,16 +4277,16 @@
     <row r="2" s="2" customFormat="1" ht="28.8" customHeight="1" spans="1:6">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="3">
-        <v>1</v>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
@@ -4288,16 +4297,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="3">
-        <v>1</v>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -4308,16 +4317,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="E4" s="3">
-        <v>1</v>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
@@ -4328,16 +4337,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="E5" s="3">
-        <v>1</v>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>8</v>
@@ -4348,16 +4357,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
+      <c r="E6" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>8</v>
@@ -4371,10 +4380,10 @@
         <v>150</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>33</v>
@@ -4388,7 +4397,7 @@
         <v>150</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D8" s="2">
         <v>5</v>
@@ -4427,19 +4436,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>5</v>
@@ -4450,10 +4459,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -4479,10 +4488,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -4508,10 +4517,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -4537,10 +4546,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -4566,10 +4575,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -4595,10 +4604,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -4624,10 +4633,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -4653,10 +4662,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="D9" s="2">
         <v>4</v>
@@ -4682,10 +4691,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D10" s="2">
         <v>5</v>
@@ -4711,10 +4720,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -4740,10 +4749,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -4769,10 +4778,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4798,10 +4807,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D14" s="2">
         <v>7</v>
@@ -4827,10 +4836,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D15" s="2">
         <v>7</v>
@@ -4856,10 +4865,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D16" s="2">
         <v>8</v>
@@ -4885,10 +4894,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D17" s="2">
         <v>8</v>
@@ -4914,10 +4923,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D18" s="2">
         <v>9</v>
@@ -4943,10 +4952,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D19" s="2">
         <v>9</v>
@@ -4972,10 +4981,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D20" s="2">
         <v>10</v>
@@ -5001,10 +5010,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D21" s="2">
         <v>10</v>
@@ -5030,10 +5039,10 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D22" s="2">
         <v>11</v>
@@ -5053,10 +5062,10 @@
         <v>26</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -5076,10 +5085,10 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -5099,10 +5108,10 @@
         <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -5163,10 +5172,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -5221,10 +5230,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -5325,10 +5334,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -5342,10 +5351,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -5365,10 +5374,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -5388,10 +5397,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -5411,10 +5420,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" t="s">
         <v>223</v>
-      </c>
-      <c r="C5" t="s">
-        <v>220</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -5434,10 +5443,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -5454,10 +5463,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -5506,16 +5515,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5523,16 +5532,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" t="s">
         <v>230</v>
       </c>
-      <c r="C3" t="s">
-        <v>227</v>
-      </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5540,13 +5549,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -5586,16 +5595,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -5638,13 +5647,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -5687,16 +5696,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -5744,16 +5753,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -5767,13 +5776,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" t="s">
         <v>249</v>
       </c>
-      <c r="C3" t="s">
-        <v>246</v>
-      </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -5822,16 +5831,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -5874,10 +5883,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -5926,13 +5935,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -6391,7 +6400,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -6405,10 +6414,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6425,10 +6434,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6437,7 +6446,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -6463,7 +6472,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -6477,10 +6486,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D2">
         <v>128</v>
@@ -6515,7 +6524,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -6529,10 +6538,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6549,10 +6558,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6561,7 +6570,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -6587,7 +6596,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -6601,10 +6610,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -6655,13 +6664,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6693,13 +6702,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -6713,10 +6722,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D2">
         <v>255</v>
@@ -6739,10 +6748,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6765,10 +6774,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -6791,10 +6800,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" t="s">
         <v>282</v>
-      </c>
-      <c r="C5" t="s">
-        <v>279</v>
       </c>
       <c r="D5">
         <v>256</v>
@@ -6832,16 +6841,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -6855,10 +6864,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6913,10 +6922,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -6963,13 +6972,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6998,7 +7007,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -7012,10 +7021,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -7032,10 +7041,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -8087,13 +8096,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8122,7 +8131,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -8136,10 +8145,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -8156,10 +8165,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -8202,10 +8211,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -8248,10 +8257,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -8294,10 +8303,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -8333,10 +8342,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -8345,7 +8354,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8353,10 +8362,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8379,10 +8388,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -8405,10 +8414,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -8431,10 +8440,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" t="s">
         <v>313</v>
-      </c>
-      <c r="C5" t="s">
-        <v>310</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -8457,10 +8466,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8483,10 +8492,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -8506,10 +8515,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -8563,13 +8572,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8598,7 +8607,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -8607,7 +8616,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8615,13 +8624,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -8664,13 +8673,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8710,13 +8719,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8820,7 +8829,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -8829,7 +8838,7 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8837,10 +8846,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8860,10 +8869,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -8906,10 +8915,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8949,10 +8958,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8992,10 +9001,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -9035,10 +9044,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -9081,10 +9090,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D2">
         <v>1.2</v>
@@ -9127,10 +9136,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -9173,10 +9182,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -9219,10 +9228,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -9255,7 +9264,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -9269,13 +9278,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -9694,7 +9703,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -9708,10 +9717,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D2">
         <v>9600</v>
@@ -9743,7 +9752,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -9757,16 +9766,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -9803,16 +9812,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -9849,16 +9858,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>362</v>
-      </c>
-      <c r="C2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -9895,10 +9904,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -9933,7 +9942,7 @@
         <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -9947,13 +9956,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -9965,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9973,13 +9982,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" t="s">
         <v>371</v>
       </c>
-      <c r="C3" t="s">
-        <v>368</v>
-      </c>
       <c r="D3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E3">
         <v>100</v>
@@ -9991,7 +10000,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -10031,10 +10040,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -10048,10 +10057,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -10083,7 +10092,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
@@ -10097,10 +10106,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -10117,10 +10126,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -10159,7 +10168,7 @@
         <v>107</v>
       </c>
       <c r="E1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -10176,10 +10185,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -10202,10 +10211,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -10228,10 +10237,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -10254,10 +10263,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" t="s">
         <v>380</v>
-      </c>
-      <c r="C5" t="s">
-        <v>377</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -10280,10 +10289,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -10306,10 +10315,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C7" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -10332,10 +10341,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -10358,10 +10367,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C9" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -10384,10 +10393,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -10407,10 +10416,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -10430,10 +10439,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C12" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -10453,10 +10462,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C13" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -10476,10 +10485,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C14" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -10499,10 +10508,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C15" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -10522,10 +10531,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C16" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -10545,10 +10554,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -10568,10 +10577,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C18" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -10591,10 +10600,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C19" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -10614,10 +10623,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C20" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -10637,10 +10646,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C21" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -10678,10 +10687,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -10695,16 +10704,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G2" t="s">
         <v>33</v>
@@ -10715,16 +10724,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" t="s">
         <v>403</v>
       </c>
-      <c r="C3" t="s">
-        <v>400</v>
-      </c>
       <c r="D3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -10738,13 +10747,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E4" t="s">
         <v>98</v>
@@ -10761,22 +10770,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D5" t="s">
         <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -11082,7 +11091,7 @@
         <v>110</v>
       </c>
       <c r="E11" s="3">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F11" s="3">
         <v>30</v>
